--- a/p6_deployment/data/argentina/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/p6_deployment/data/argentina/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D401"/>
+  <dimension ref="A1:D478"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3176,61 +3176,61 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>I9WKqwWD</t>
+          <t>ns28GgKH</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>U5BaezVP</t>
+          <t>8djHEXlU</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>GQTCXWxJ</t>
+          <t>MaGjTW3N</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3242,232 +3242,232 @@
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>j3vZLZw7</t>
+          <t>hr7MNARp</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>YsYixeOm</t>
+          <t>fmo5nf4o</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>2.25</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>nobRjfws</t>
+          <t>vHb0IFk5</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>xCnMsH0Q</t>
+          <t>r9HnUClH</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>d0VOrcoK</t>
+          <t>GMFfSjJT</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>QycVkEhm</t>
+          <t>U5iDFDZN</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>46rwLggD</t>
+          <t>Ywb4HZ4B</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>vLYmwy9s</t>
+          <t>nsOwWYJ4</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
           <t>2.75</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>U9R0zZh0</t>
+          <t>fDUeLH5n</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>noxdyFwf</t>
+          <t>tpLVXfkh</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>rDizkY7g</t>
+          <t>KUWMZGKu</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3477,283 +3477,283 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>8vkUMFO0</t>
+          <t>bLVQYzzn</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>80Q4Zh86</t>
+          <t>Y3TaKyLh</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>xzV8YCNC</t>
+          <t>QXMsVhZA</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>UmjQNe9f</t>
+          <t>0QadJeza</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>SrG895lp</t>
+          <t>hKOZWE4b</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>M97qBIPl</t>
+          <t>CS1rsvB8</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
           <t>3.60</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>nkYuEotT</t>
+          <t>W8pDRbBL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>8Q9e8G97</t>
+          <t>8feiuIuL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>G4d3VnB3</t>
+          <t>6kwvWD27</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>prgvXan8</t>
+          <t>pM9dJzJ1</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
           <t>3.25</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>OYirWJ1E</t>
+          <t>EXZHQIQR</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>Kx3fX8ti</t>
+          <t>bPD0IfY7</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>0EoMOyfl</t>
+          <t>jJ0ntbQE</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3763,90 +3763,90 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>GtAkUcWQ</t>
+          <t>O6LmLdlk</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>IeinVwHK</t>
+          <t>2cKiKG3e</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>2LfBTQuG</t>
+          <t>ptxrVXHD</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>6ZEC8P3j</t>
+          <t>4QtNZe3r</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3858,149 +3858,149 @@
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>zDBmAxue</t>
+          <t>GtMqMxZr</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>voIvCbAr</t>
+          <t>xGYZWgm1</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>fee7U6Q9</t>
+          <t>lE2OwQLD</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>MNnIPHvr</t>
+          <t>nofevxeR</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>UZAi9df1</t>
+          <t>0jViMcjt</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>Yu7bWSec</t>
+          <t>G0pRYFIl</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>hSM4GJpU</t>
+          <t>bPZVXZXf</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4012,122 +4012,122 @@
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>CCwHJkCi</t>
+          <t>KzK40MCM</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>E1gdK1o5</t>
+          <t>Ors5TKt9</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>tnrLI9Rc</t>
+          <t>dIMXgKkj</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>OC0qN31n</t>
+          <t>Uq0E6cZe</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>hhh0JL0B</t>
+          <t>phr1U0R2</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>fcMV3t1O</t>
+          <t>lC9JHNsc</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4137,19 +4137,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>YLvDKVdo</t>
+          <t>zN0A7wKk</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4159,19 +4159,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>KvfhLsWb</t>
+          <t>Wf5vDadS</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4181,156 +4181,156 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>pM1uOqnt</t>
+          <t>8zaI5Hl2</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>b5N0HaVN</t>
+          <t>h46zEusM</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>UmEWBwgo</t>
+          <t>2FDNGsc3</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>6yjlMNGh</t>
+          <t>I5t9SvdF</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>EyzYF7BG</t>
+          <t>z9Lygv5d</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.30</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>YmLZ20GU</t>
+          <t>G65ze0zp</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>21WTGmdA</t>
+          <t>EcJ8atSS</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4342,56 +4342,56 @@
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>8bZyFRQM</t>
+          <t>pv3SF1C9</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>KEOdIuGH</t>
+          <t>6XF012cG</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>KxsPHTt4</t>
+          <t>xxr78J4q</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4401,212 +4401,212 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>CYWQ4MoI</t>
+          <t>OU1WELRF</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>SpVE7O1a</t>
+          <t>dbQG1Bia</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>rZGSeR2m</t>
+          <t>WGITb9yI</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>0zozF69P</t>
+          <t>2yRC2ixg</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>WIy69pXn</t>
+          <t>zmp1t1Lj</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>lYbfEZIE</t>
+          <t>40ox9gaP</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>xdx2AQHt</t>
+          <t>69X34D7t</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>A9zA84ng</t>
+          <t>UTgnnWiC</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>xdGWfoIg</t>
+          <t>zkPK0V65</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>Kv8mi3HI</t>
+          <t>jqrepAMO</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4616,46 +4616,46 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>0bTM52WB</t>
+          <t>lYM83XMn</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>4rIOd7ms</t>
+          <t>Chqioj7I</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4665,300 +4665,300 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>As0jFF38</t>
+          <t>OCtcss6p</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>bV6ijNWO</t>
+          <t>O8Qe2rrA</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>jaKzf5Xa</t>
+          <t>GrNm44Dc</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>CE8qhq2C</t>
+          <t>pIRi3OS3</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>dvC8jWQ7</t>
+          <t>xhOq5pbi</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>YN9ugPn6</t>
+          <t>hQJPakMB</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>6yUI6rH5</t>
+          <t>M3jvlhNa</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>6eEQbfJR</t>
+          <t>GQkrmCx6</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>bXHUvZRe</t>
+          <t>I9WKqwWD</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>OWOLaz4L</t>
+          <t>U5BaezVP</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
           <t>2.88</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>pQyfoykS</t>
+          <t>GQTCXWxJ</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>xOGYwgs2</t>
+          <t>j3vZLZw7</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>b9Zslw59</t>
+          <t>YsYixeOm</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.10</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>j7EMtecq</t>
+          <t>nobRjfws</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -4980,7 +4980,7 @@
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>6ZxjnHZL</t>
+          <t>xCnMsH0Q</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4995,437 +4995,437 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>GppwkJk3</t>
+          <t>d0VOrcoK</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>x0YomcKF</t>
+          <t>QycVkEhm</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>4.10</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>bgg5iCB1</t>
+          <t>46rwLggD</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>xv5dgYtk</t>
+          <t>vLYmwy9s</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
           <t>2.90</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>ATKH0GlF</t>
+          <t>U9R0zZh0</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>GU30hhde</t>
+          <t>noxdyFwf</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.10</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>4AtZkazc</t>
+          <t>rDizkY7g</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>840hfERr</t>
+          <t>8vkUMFO0</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>4AIQuFCk</t>
+          <t>80Q4Zh86</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>xGM92xK2</t>
+          <t>xzV8YCNC</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>G6LD1dZ8</t>
+          <t>UmjQNe9f</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>foxezhfR</t>
+          <t>SrG895lp</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>QRiXYisF</t>
+          <t>M97qBIPl</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>zyK0HPBs</t>
+          <t>nkYuEotT</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>Uu8UEWkq</t>
+          <t>8Q9e8G97</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>zceyU2em</t>
+          <t>G4d3VnB3</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>hEgPzEC2</t>
+          <t>prgvXan8</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>GdAtCUZ1</t>
+          <t>OYirWJ1E</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>hxhCZOXP</t>
+          <t>Kx3fX8ti</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>d6dXUrts</t>
+          <t>0EoMOyfl</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5435,63 +5435,63 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>rqCYDj5k</t>
+          <t>GtAkUcWQ</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>x6BxDAKe</t>
+          <t>IeinVwHK</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>nu1MC1QC</t>
+          <t>2LfBTQuG</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5501,349 +5501,349 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>W4hTZXR8</t>
+          <t>6ZEC8P3j</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>dj89F3tf</t>
+          <t>zDBmAxue</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
           <t>3.00</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>UJfuTMAg</t>
+          <t>voIvCbAr</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>Ia95GqRm</t>
+          <t>fee7U6Q9</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>4GBHDsB6</t>
+          <t>MNnIPHvr</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>QPCDENe0</t>
+          <t>UZAi9df1</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>Eog8z5IJ</t>
+          <t>Yu7bWSec</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>0r5QBLuJ</t>
+          <t>hSM4GJpU</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>8l04AHbc</t>
+          <t>CCwHJkCi</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>bwgH7FrG</t>
+          <t>E1gdK1o5</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>jXHfLYCF</t>
+          <t>tnrLI9Rc</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>ShNHnE6j</t>
+          <t>OC0qN31n</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>4zdP5gDS</t>
+          <t>hhh0JL0B</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>EkJDmfip</t>
+          <t>fcMV3t1O</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>ObV1JCsS</t>
+          <t>YLvDKVdo</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>Uc10Bcqi</t>
+          <t>KvfhLsWb</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5853,41 +5853,41 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.35</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>p8WcKhSL</t>
+          <t>pM1uOqnt</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>2By0aijd</t>
+          <t>b5N0HaVN</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5897,173 +5897,173 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>OKxd0Xzj</t>
+          <t>UmEWBwgo</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>dAWohzqT</t>
+          <t>6yjlMNGh</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>GEPsOzTd</t>
+          <t>EyzYF7BG</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>CtJjMEc9</t>
+          <t>YmLZ20GU</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>ADdL6ZcM</t>
+          <t>21WTGmdA</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>6qri1DLq</t>
+          <t>8bZyFRQM</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>xO489yE3</t>
+          <t>KEOdIuGH</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>UHToNfr3</t>
+          <t>KxsPHTt4</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6073,58 +6073,58 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>GE3C8eT9</t>
+          <t>CYWQ4MoI</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>b3x8twpH</t>
+          <t>SpVE7O1a</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>Qkv0raF4</t>
+          <t>rZGSeR2m</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6134,393 +6134,393 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>8SOTcvFi</t>
+          <t>0zozF69P</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>URULv7oD</t>
+          <t>WIy69pXn</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.10</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>4fIxdIq4</t>
+          <t>lYbfEZIE</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>dleBucaN</t>
+          <t>xdx2AQHt</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>bHHtexaA</t>
+          <t>A9zA84ng</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
         <is>
-          <t>IJXsgGTM</t>
+          <t>xdGWfoIg</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t>z1omo1Vo</t>
+          <t>Kv8mi3HI</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t>8ITPwR0J</t>
+          <t>0bTM52WB</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t>vDpGvHET</t>
+          <t>4rIOd7ms</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t>4tw4sJUA</t>
+          <t>As0jFF38</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t>x8GpfdEG</t>
+          <t>bV6ijNWO</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>8Eqequ0b</t>
+          <t>jaKzf5Xa</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>jiEYdbUc</t>
+          <t>CE8qhq2C</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>tMWszyNp</t>
+          <t>dvC8jWQ7</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>UNpipLph</t>
+          <t>YN9ugPn6</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>UyQPbKao</t>
+          <t>6yUI6rH5</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>McsqnsGu</t>
+          <t>6eEQbfJR</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>xzudZj8s</t>
+          <t>bXHUvZRe</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -6542,183 +6542,183 @@
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>0ns9s91f</t>
+          <t>OWOLaz4L</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>MRE8EAX7</t>
+          <t>pQyfoykS</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>8UZrwfA8</t>
+          <t>xOGYwgs2</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>U76vST17</t>
+          <t>b9Zslw59</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>trYjyYvL</t>
+          <t>j7EMtecq</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>nqHZS9n1</t>
+          <t>6ZxjnHZL</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>M1VHumW6</t>
+          <t>GppwkJk3</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>0SENVB2r</t>
+          <t>x0YomcKF</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>YycUli9K</t>
+          <t>bgg5iCB1</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -6728,46 +6728,46 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>vJDRUVHl</t>
+          <t>xv5dgYtk</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>nLYnxEPE</t>
+          <t>ATKH0GlF</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -6777,102 +6777,102 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>8hIVTkXf</t>
+          <t>GU30hhde</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>rBWDtTG0</t>
+          <t>4AtZkazc</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>trArRmHD</t>
+          <t>840hfERr</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>nqw5rknl</t>
+          <t>4AIQuFCk</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>jDiZmBOQ</t>
+          <t>xGM92xK2</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -6882,315 +6882,315 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>hMw1qVWs</t>
+          <t>G6LD1dZ8</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>fobQkXgE</t>
+          <t>foxezhfR</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>M3WLNEAL</t>
+          <t>QRiXYisF</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>lEv9QGQ2</t>
+          <t>zyK0HPBs</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>zBCdHCmk</t>
+          <t>Uu8UEWkq</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>lEG0GW2e</t>
+          <t>zceyU2em</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>ryG4FjI1</t>
+          <t>hEgPzEC2</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>dKiN2DYe</t>
+          <t>GdAtCUZ1</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>rDBn9FeS</t>
+          <t>hxhCZOXP</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>0lrDPzt9</t>
+          <t>d6dXUrts</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>MwLRDwsc</t>
+          <t>rqCYDj5k</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>noIwByRF</t>
+          <t>x6BxDAKe</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>U97rAetM</t>
+          <t>nu1MC1QC</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>0hbE4Z3q</t>
+          <t>W4hTZXR8</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -7202,56 +7202,56 @@
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>0UJVCcd3</t>
+          <t>dj89F3tf</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>vqcI3gJk</t>
+          <t>UJfuTMAg</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>rDXHOfeF</t>
+          <t>Ia95GqRm</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7261,46 +7261,46 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>zBjR1Xm2</t>
+          <t>4GBHDsB6</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>jwyQMYPR</t>
+          <t>QPCDENe0</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -7312,452 +7312,452 @@
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>8fJZBHB9</t>
+          <t>Eog8z5IJ</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>hnNiIhYr</t>
+          <t>0r5QBLuJ</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>15.00</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>KYtqkf4d</t>
+          <t>8l04AHbc</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>OjLay0L3</t>
+          <t>bwgH7FrG</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
           <t>2.30</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>6Vxujzkj</t>
+          <t>jXHfLYCF</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>hWCGXHKS</t>
+          <t>ShNHnE6j</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>CGgmSerj</t>
+          <t>4zdP5gDS</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>UF6dxt6c</t>
+          <t>EkJDmfip</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>zqG78r5H</t>
+          <t>ObV1JCsS</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>zHP5FIbp</t>
+          <t>Uc10Bcqi</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.30</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>I7L29OkB</t>
+          <t>p8WcKhSL</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>vHMbA4z5</t>
+          <t>2By0aijd</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>2sK3zKzA</t>
+          <t>OKxd0Xzj</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>b9DCYc5M</t>
+          <t>dAWohzqT</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
           <t>3.10</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>j7hiRFcd</t>
+          <t>GEPsOzTd</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.85</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>fuarTyTq</t>
+          <t>CtJjMEc9</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>lKT9ExEj</t>
+          <t>ADdL6ZcM</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>p698ZwjG</t>
+          <t>6qri1DLq</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>IywvKbjT</t>
+          <t>xO489yE3</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>C8wyiGZq</t>
+          <t>UHToNfr3</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>jP7hwMji</t>
+          <t>GE3C8eT9</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -7767,200 +7767,200 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t>pfNfBpLb</t>
+          <t>b3x8twpH</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t>fchEP2Mi</t>
+          <t>Qkv0raF4</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t>Sj0S1aUp</t>
+          <t>8SOTcvFi</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
         <is>
-          <t>M9qVLKLG</t>
+          <t>URULv7oD</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
         <is>
-          <t>ldoNNti4</t>
+          <t>4fIxdIq4</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
         <is>
-          <t>h6oUfPzI</t>
+          <t>dleBucaN</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
         <is>
-          <t>jRxaJRaI</t>
+          <t>bHHtexaA</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
         <is>
-          <t>rJpRM06A</t>
+          <t>IJXsgGTM</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="inlineStr">
         <is>
-          <t>0xpnMTFa</t>
+          <t>z1omo1Vo</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -7972,188 +7972,188 @@
     <row r="344">
       <c r="A344" s="1" t="inlineStr">
         <is>
-          <t>4pFnD6jn</t>
+          <t>8ITPwR0J</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="inlineStr">
         <is>
-          <t>ELZxg35U</t>
+          <t>vDpGvHET</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="inlineStr">
         <is>
-          <t>QgGrEnyt</t>
+          <t>4tw4sJUA</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="inlineStr">
         <is>
-          <t>n94iCQ5h</t>
+          <t>x8GpfdEG</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="inlineStr">
         <is>
-          <t>G6gAQr7o</t>
+          <t>8Eqequ0b</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="inlineStr">
         <is>
-          <t>vovzLvyN</t>
+          <t>jiEYdbUc</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="inlineStr">
         <is>
-          <t>faqjLmV5</t>
+          <t>tMWszyNp</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="inlineStr">
         <is>
-          <t>xMsJOMyb</t>
+          <t>UNpipLph</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="inlineStr">
         <is>
-          <t>82mfK7pC</t>
+          <t>UyQPbKao</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -8163,344 +8163,344 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="inlineStr">
         <is>
-          <t>zVzZgqjO</t>
+          <t>McsqnsGu</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="inlineStr">
         <is>
-          <t>W0vBUi8J</t>
+          <t>xzudZj8s</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="inlineStr">
         <is>
-          <t>rubG8Ao0</t>
+          <t>0ns9s91f</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="inlineStr">
         <is>
-          <t>2qVtPVVt</t>
+          <t>MRE8EAX7</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="inlineStr">
         <is>
-          <t>p4rFTBNP</t>
+          <t>8UZrwfA8</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="inlineStr">
         <is>
-          <t>hQTC0T6t</t>
+          <t>U76vST17</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="inlineStr">
         <is>
-          <t>88j4BC1s</t>
+          <t>trYjyYvL</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="inlineStr">
         <is>
-          <t>QwSKb7yg</t>
+          <t>nqHZS9n1</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="inlineStr">
         <is>
-          <t>G4xo59bP</t>
+          <t>M1VHumW6</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="inlineStr">
         <is>
-          <t>MoorN90g</t>
+          <t>0SENVB2r</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="inlineStr">
         <is>
-          <t>6kqIcRja</t>
+          <t>YycUli9K</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="inlineStr">
         <is>
-          <t>nmTGamMn</t>
+          <t>vJDRUVHl</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="inlineStr">
         <is>
-          <t>j51O6lGC</t>
+          <t>nLYnxEPE</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="inlineStr">
         <is>
-          <t>tzUpOkom</t>
+          <t>8hIVTkXf</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="inlineStr">
         <is>
-          <t>ptrMdo65</t>
+          <t>rBWDtTG0</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="inlineStr">
         <is>
-          <t>Ue0S58VI</t>
+          <t>trArRmHD</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -8515,19 +8515,19 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="inlineStr">
         <is>
-          <t>0G8B9jWg</t>
+          <t>nqw5rknl</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -8537,709 +8537,2403 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="inlineStr">
         <is>
-          <t>2Vk8AWGm</t>
+          <t>jDiZmBOQ</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="inlineStr">
         <is>
-          <t>v3sQe5LB</t>
+          <t>hMw1qVWs</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="inlineStr">
         <is>
-          <t>MVdK7U06</t>
+          <t>fobQkXgE</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="inlineStr">
         <is>
-          <t>lO9XGYwK</t>
+          <t>M3WLNEAL</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="inlineStr">
         <is>
-          <t>fVVEckdk</t>
+          <t>lEv9QGQ2</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="inlineStr">
         <is>
-          <t>EBIz3ETH</t>
+          <t>zBCdHCmk</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="inlineStr">
         <is>
-          <t>lUWIFiDN</t>
+          <t>lEG0GW2e</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="inlineStr">
         <is>
-          <t>WCI8JFQ6</t>
+          <t>ryG4FjI1</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="inlineStr">
         <is>
-          <t>hhQXRe3K</t>
+          <t>dKiN2DYe</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="inlineStr">
         <is>
-          <t>C4DC8Iat</t>
+          <t>rDBn9FeS</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="inlineStr">
         <is>
-          <t>AwCq1hbU</t>
+          <t>0lrDPzt9</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="inlineStr">
         <is>
-          <t>SErAHDrB</t>
+          <t>MwLRDwsc</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="inlineStr">
         <is>
-          <t>KCNlAVzo</t>
+          <t>noIwByRF</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="inlineStr">
         <is>
-          <t>0QqfjypC</t>
+          <t>U97rAetM</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="inlineStr">
         <is>
-          <t>Ywr2lFEO</t>
+          <t>0hbE4Z3q</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="inlineStr">
         <is>
-          <t>tCcpyBac</t>
+          <t>0UJVCcd3</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="inlineStr">
         <is>
-          <t>KUGK6dUh</t>
+          <t>vqcI3gJk</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="inlineStr">
         <is>
-          <t>Y3ZExOz2</t>
+          <t>rDXHOfeF</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>7.40</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="inlineStr">
         <is>
-          <t>S2jWpnTL</t>
+          <t>zBjR1Xm2</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="inlineStr">
         <is>
-          <t>MHu2JZDb</t>
+          <t>jwyQMYPR</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="inlineStr">
         <is>
-          <t>QkngLeqn</t>
+          <t>8fJZBHB9</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>10.50</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="inlineStr">
         <is>
-          <t>Q3FcD77j</t>
+          <t>hnNiIhYr</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="inlineStr">
         <is>
-          <t>bkaHXyg5</t>
+          <t>KYtqkf4d</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="inlineStr">
         <is>
-          <t>nDGgEmhp</t>
+          <t>OjLay0L3</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="inlineStr">
         <is>
-          <t>MPB5aorF</t>
+          <t>6Vxujzkj</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="inlineStr">
         <is>
-          <t>hhd9ZcOh</t>
+          <t>hWCGXHKS</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
           <t>4.00</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="inlineStr">
         <is>
-          <t>zZdlzVE3</t>
+          <t>CGgmSerj</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="inlineStr">
         <is>
-          <t>z9Dc17D2</t>
+          <t>UF6dxt6c</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="inlineStr">
         <is>
-          <t>KxRhXSbM</t>
+          <t>zqG78r5H</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="inlineStr">
         <is>
-          <t>vsbJmlq3</t>
+          <t>zHP5FIbp</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="inlineStr">
         <is>
-          <t>jLHOR6Mq</t>
+          <t>I7L29OkB</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="inlineStr">
         <is>
+          <t>vHMbA4z5</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>2sK3zKzA</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>b9DCYc5M</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>j7hiRFcd</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>fuarTyTq</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>lKT9ExEj</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>p698ZwjG</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>IywvKbjT</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>C8wyiGZq</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>jP7hwMji</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>pfNfBpLb</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>fchEP2Mi</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>Sj0S1aUp</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>M9qVLKLG</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>ldoNNti4</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>h6oUfPzI</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>jRxaJRaI</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>rJpRM06A</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>0xpnMTFa</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>4pFnD6jn</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>ELZxg35U</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>QgGrEnyt</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>n94iCQ5h</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>G6gAQr7o</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>vovzLvyN</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>faqjLmV5</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>xMsJOMyb</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>82mfK7pC</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>zVzZgqjO</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>W0vBUi8J</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>rubG8Ao0</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2qVtPVVt</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>p4rFTBNP</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>hQTC0T6t</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>88j4BC1s</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>QwSKb7yg</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>G4xo59bP</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>MoorN90g</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>6kqIcRja</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>nmTGamMn</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>j51O6lGC</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>tzUpOkom</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>ptrMdo65</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>Ue0S58VI</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>0G8B9jWg</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2Vk8AWGm</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>v3sQe5LB</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>MVdK7U06</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>lO9XGYwK</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>zL5yYYSi</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>fVVEckdk</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>5.28</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>9.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>EBIz3ETH</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>lUWIFiDN</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>WCI8JFQ6</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>4.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>hhQXRe3K</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>C4DC8Iat</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>AwCq1hbU</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>SErAHDrB</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>KCNlAVzo</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>0QqfjypC</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>11.40</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>5.90</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>Ywr2lFEO</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>tCcpyBac</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>KUGK6dUh</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>Y3ZExOz2</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>7.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>S2jWpnTL</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>MHu2JZDb</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>QkngLeqn</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>10.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>Q3FcD77j</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>bkaHXyg5</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>nDGgEmhp</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>MPB5aorF</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>hhd9ZcOh</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>zZdlzVE3</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>z9Dc17D2</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>KxRhXSbM</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>vsbJmlq3</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr">
+        <is>
+          <t>jLHOR6Mq</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr">
+        <is>
           <t>tElMWe8B</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr">
+      <c r="B478" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="C401" t="inlineStr">
+      <c r="C478" t="inlineStr">
         <is>
           <t>7.00</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr">
+      <c r="D478" t="inlineStr">
         <is>
           <t>14.00</t>
         </is>
